--- a/backtest_runs/20260410_193731/by_symbol/ATIL/ATIL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ATIL/ATIL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>103948.5</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>103948.5</v>
@@ -909,7 +909,7 @@
         <v>-2981.25</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>102159.75</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>105962.5</v>
@@ -1185,7 +1185,7 @@
         <v>-1285.249999999998</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>104995.25</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>104995.25</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>104995.25</v>
@@ -1415,7 +1415,7 @@
         <v>-1788.749999999992</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>103206.5</v>
@@ -1461,7 +1461,7 @@
         <v>-8851.000000000009</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>94355.50000000001</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>94355.50000000001</v>
@@ -1553,7 +1553,7 @@
         <v>-371.0000000000015</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>93984.50000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-1152.749999999987</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>95468.50000000001</v>
